--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1275</v>
+        <v>6.2052</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2006</v>
+        <v>6.5754</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0731</v>
+        <v>-0.3702</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8213</v>
+        <v>7.9288</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0655</v>
+        <v>5.1813</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7558</v>
+        <v>2.7474</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4236</v>
+        <v>8.691800000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9801</v>
+        <v>6.1708</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4435</v>
+        <v>2.521</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.763</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9146</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3123</v>
+        <v>0.2264</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3941</v>
+        <v>-0.3894</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4822</v>
+        <v>-0.4485</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0881</v>
+        <v>0.0591</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.8998</v>
+        <v>-1.9184</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1596</v>
+        <v>-2.1979</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1827</v>
+        <v>5.2613</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9282</v>
+        <v>7.4407</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7456</v>
+        <v>-2.1795</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4226</v>
+        <v>3.4149</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0662</v>
+        <v>5.1254</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6436</v>
+        <v>-1.7105</v>
       </c>
       <c r="J3" t="n">
-        <v>5.882</v>
+        <v>6.0989</v>
       </c>
       <c r="K3" t="n">
-        <v>7.038</v>
+        <v>7.2253</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4593</v>
+        <v>-2.684</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4875</v>
+        <v>-0.5841</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9413</v>
+        <v>0.9058</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.191</v>
+        <v>-0.155</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1323</v>
+        <v>1.0609</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2191</v>
+        <v>2.3037</v>
       </c>
       <c r="W3" t="n">
-        <v>5.2384</v>
+        <v>5.3916</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.0193</v>
+        <v>-3.0879</v>
       </c>
     </row>
     <row r="4">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1997</v>
+        <v>1.2237</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2137</v>
+        <v>-0.2364</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1089</v>
+        <v>-0.1031</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1048</v>
+        <v>-0.1333</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.173</v>
+        <v>-0.1966</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3086</v>
+        <v>-0.3295</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3286</v>
+        <v>-0.35</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,22 +844,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3808</v>
+        <v>-0.3709</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2519</v>
+        <v>-0.2473</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="6">
@@ -873,67 +873,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3005</v>
+        <v>-0.3769</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4002</v>
+        <v>-0.3723</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09959999999999999</v>
+        <v>-0.0046</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0076</v>
+        <v>-0.0631</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.446</v>
+        <v>-0.4958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4537</v>
+        <v>0.4327</v>
       </c>
       <c r="J6" t="n">
-        <v>0.18</v>
+        <v>0.1842</v>
       </c>
       <c r="K6" t="n">
-        <v>0.14</v>
+        <v>0.1437</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1723</v>
+        <v>-0.2473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9485</v>
+        <v>-0.9212</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3684</v>
+        <v>-0.3647</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="7">
@@ -951,67 +951,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3005</v>
+        <v>-0.3769</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4002</v>
+        <v>-0.3723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09959999999999999</v>
+        <v>-0.0046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0076</v>
+        <v>-0.0631</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.446</v>
+        <v>-0.4958</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4537</v>
+        <v>0.4327</v>
       </c>
       <c r="J7" t="n">
-        <v>0.18</v>
+        <v>0.1842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.14</v>
+        <v>0.1437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1723</v>
+        <v>-0.2473</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9485</v>
+        <v>-0.9212</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3684</v>
+        <v>-0.3647</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="8">
@@ -1029,67 +1029,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5565</v>
+        <v>-0.7047</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7604</v>
+        <v>1.9498</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3169</v>
+        <v>-2.6546</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.334</v>
+        <v>-1.4523</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7549</v>
+        <v>-0.801</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2035</v>
+        <v>1.2805</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1997</v>
+        <v>1.2316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5375</v>
+        <v>-2.7327</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7787</v>
+        <v>-1.8828</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7587</v>
+        <v>-0.8499</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1428</v>
+        <v>-0.1482</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4822</v>
+        <v>-0.4485</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3395</v>
+        <v>0.3003</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0392</v>
+        <v>1.1179</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="9">
@@ -1107,64 +1107,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0825</v>
+        <v>-1.1112</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.439</v>
+        <v>-0.3152</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6435</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7481</v>
+        <v>-0.8065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2156</v>
+        <v>0.215</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9637</v>
+        <v>-1.0215</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.9355</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8016</v>
+        <v>0.8544</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6297</v>
+        <v>-1.742</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0437</v>
+        <v>-1.1026</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5942</v>
+        <v>-0.5841</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0141</v>
+        <v>-0.0276</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1185,67 +1185,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4449</v>
+        <v>-2.387</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9659</v>
+        <v>-2.6274</v>
       </c>
       <c r="F10" t="n">
-        <v>0.521</v>
+        <v>0.2404</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7553</v>
+        <v>-0.7761</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9533</v>
+        <v>-1.9674</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1979</v>
+        <v>1.1913</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1891</v>
+        <v>1.3448</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0254</v>
+        <v>0.1207</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1636</v>
+        <v>1.2241</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9444</v>
+        <v>-2.1209</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9787</v>
+        <v>-2.0881</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3491</v>
+        <v>-1.3167</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3536</v>
+        <v>-1.2985</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0045</v>
+        <v>-0.0182</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8601</v>
+        <v>1.8479</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6604</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="11">
@@ -1263,67 +1263,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6082</v>
+        <v>-2.6401</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5337</v>
+        <v>-1.2921</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0745</v>
+        <v>-1.348</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5884</v>
+        <v>-1.6342</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4475</v>
+        <v>0.3838</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0359</v>
+        <v>-2.018</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2507</v>
+        <v>-0.1173</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8195</v>
+        <v>1.8679</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0702</v>
+        <v>-1.9852</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3377</v>
+        <v>-1.5169</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3719</v>
+        <v>-1.4841</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2001</v>
+        <v>-1.1654</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4822</v>
+        <v>-0.4485</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7179</v>
+        <v>-0.7168</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2196</v>
+        <v>-1.2563</v>
       </c>
     </row>
     <row r="12">
@@ -1341,64 +1341,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3896</v>
+        <v>-3.3558</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4101</v>
+        <v>-2.2931</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9795</v>
+        <v>-1.0626</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5328</v>
+        <v>-1.5766</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.011</v>
+        <v>-1.0253</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2181</v>
+        <v>-0.1924</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2181</v>
+        <v>-0.1924</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3147</v>
+        <v>-1.3842</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7929</v>
+        <v>-0.8329</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9162</v>
+        <v>-0.8902</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4651</v>
+        <v>-0.4574</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1419,28 +1419,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8396</v>
+        <v>-3.804</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2572</v>
+        <v>-1.1211</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5824</v>
+        <v>-2.6828</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.8263</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1455,31 +1455,31 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6768</v>
+        <v>0.6493</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6768</v>
+        <v>0.6493</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.2592</v>
+        <v>-3.3321</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.2592</v>
+        <v>-3.3321</v>
       </c>
     </row>
     <row r="14">
@@ -1497,67 +1497,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.7204</v>
+        <v>-10.7427</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.4714</v>
+        <v>-5.2617</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.2491</v>
+        <v>-5.4811</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.9264</v>
+        <v>-5.9669</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4509</v>
+        <v>-1.4769</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.4756</v>
+        <v>-4.4901</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.5684</v>
+        <v>-2.4486</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0636</v>
+        <v>0.1284</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.632</v>
+        <v>-2.577</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.358</v>
+        <v>-3.5183</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5145</v>
+        <v>-1.6052</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8435</v>
+        <v>-1.9131</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.794</v>
+        <v>-0.7758</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9024</v>
+        <v>-0.8657</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1084</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="15">
@@ -1575,67 +1575,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.9465</v>
+        <v>-13.0455</v>
       </c>
       <c r="E15" t="n">
-        <v>1.102300000000001</v>
+        <v>3.431299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.0492</v>
+        <v>-16.4768</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1442</v>
+        <v>0.8582999999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9431</v>
+        <v>5.905599999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.7989</v>
+        <v>-5.0475</v>
       </c>
       <c r="J15" t="n">
-        <v>16.8657</v>
+        <v>18.0321</v>
       </c>
       <c r="K15" t="n">
-        <v>18.353</v>
+        <v>19.1567</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4874</v>
+        <v>-1.1246</v>
       </c>
       <c r="M15" t="n">
-        <v>-15.7212</v>
+        <v>-17.1737</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.4097</v>
+        <v>-13.2506</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3113</v>
+        <v>-3.9231</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.001</v>
+        <v>-3.8948</v>
       </c>
       <c r="Q15" t="n">
-        <v>-19.0055</v>
+        <v>-18.5001</v>
       </c>
       <c r="R15" t="n">
-        <v>15.0042</v>
+        <v>14.6053</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.0502</v>
+        <v>-5.928</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.214</v>
+        <v>-5.890700000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1638</v>
+        <v>-0.03720000000000011</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.0394</v>
+        <v>-4.0809</v>
       </c>
       <c r="W15" t="n">
-        <v>9.4566</v>
+        <v>9.7902</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.4959</v>
+        <v>-13.871</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2052</v>
+        <v>6.1333</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5754</v>
+        <v>6.4757</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3702</v>
+        <v>-0.3423</v>
       </c>
       <c r="G2" t="n">
         <v>7.9288</v>
@@ -610,13 +610,13 @@
         <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3894</v>
+        <v>-0.4612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4485</v>
+        <v>-0.5482</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0591</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-1.9184</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2613</v>
+        <v>4.3455</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4407</v>
+        <v>6.9424</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1795</v>
+        <v>-2.5969</v>
       </c>
       <c r="G3" t="n">
         <v>3.4149</v>
@@ -688,13 +688,13 @@
         <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9058</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.155</v>
+        <v>-0.6534</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0609</v>
+        <v>0.6435</v>
       </c>
       <c r="V3" t="n">
         <v>2.3037</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2364</v>
+        <v>-0.0268</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1031</v>
+        <v>-0.2726</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1333</v>
+        <v>0.2459</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1966</v>
+        <v>-0.0631</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3295</v>
+        <v>-0.4958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1329</v>
+        <v>0.4327</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0205</v>
+        <v>0.1842</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0205</v>
+        <v>0.1437</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2171</v>
+        <v>-0.2473</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.35</v>
+        <v>-0.6394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1329</v>
+        <v>0.3921</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3709</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1237</v>
+        <v>-0.4568</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2473</v>
+        <v>-0.1142</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3311</v>
+        <v>-0.3663</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3311</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="6">
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3769</v>
+        <v>-0.0268</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3723</v>
+        <v>-0.2726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0046</v>
+        <v>0.2459</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0631</v>
@@ -918,13 +918,13 @@
         <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9212</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.4568</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3647</v>
+        <v>-0.1142</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3663</v>
@@ -939,7 +939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,73 +951,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3769</v>
+        <v>-0.2086</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3723</v>
+        <v>-0.1031</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0046</v>
+        <v>-0.1055</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0631</v>
+        <v>-0.1966</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4958</v>
+        <v>-0.3295</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4327</v>
+        <v>0.1329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1842</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1437</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2473</v>
+        <v>-0.2171</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6394</v>
+        <v>-0.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3921</v>
+        <v>0.1329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9212</v>
+        <v>-0.3431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5565</v>
+        <v>-0.1237</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3647</v>
+        <v>-0.2194</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3663</v>
+        <v>0.3311</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3663</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MANES CARRETERO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,73 +1029,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7047</v>
+        <v>-0.9837</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9498</v>
+        <v>-0.2155</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6546</v>
+        <v>-0.7681</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4523</v>
+        <v>-0.8065</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6513</v>
+        <v>0.215</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.801</v>
+        <v>-1.0215</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2805</v>
+        <v>0.9355</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2316</v>
+        <v>0.8544</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0489</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7327</v>
+        <v>-1.742</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8828</v>
+        <v>-0.6394</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8499</v>
+        <v>-1.1026</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5579</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1482</v>
+        <v>-0.4566</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4485</v>
+        <v>-0.4568</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3003</v>
+        <v>0.0002</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6621</v>
+        <v>0.2795</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1179</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>M. MANES CARRETERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,67 +1107,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1112</v>
+        <v>-1.071</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3152</v>
+        <v>1.7505</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-2.8215</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8065</v>
+        <v>-1.4523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.215</v>
+        <v>-0.6513</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0215</v>
+        <v>-0.801</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9355</v>
+        <v>1.2805</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8544</v>
+        <v>1.2316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.742</v>
+        <v>-2.7327</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6394</v>
+        <v>-1.8828</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1026</v>
+        <v>-0.8499</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9737</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5841</v>
+        <v>-0.5145</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>-0.6479</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0276</v>
+        <v>0.1333</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2795</v>
+        <v>-0.6621</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2795</v>
+        <v>1.1179</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="10">
@@ -1185,13 +1185,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.387</v>
+        <v>-1.9048</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6274</v>
+        <v>-2.2287</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2404</v>
+        <v>0.3238</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7761</v>
@@ -1230,13 +1230,13 @@
         <v>1.7526</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3167</v>
+        <v>-0.8346</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2985</v>
+        <v>-0.8998</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0182</v>
+        <v>0.0653</v>
       </c>
       <c r="V10" t="n">
         <v>1.8479</v>
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6401</v>
+        <v>-2.4777</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2921</v>
+        <v>-1.4914</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.348</v>
+        <v>-0.9863</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6342</v>
@@ -1308,13 +1308,13 @@
         <v>2.1421</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1654</v>
+        <v>-1.003</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4485</v>
+        <v>-0.6479</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7168</v>
+        <v>-0.3551</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0353</v>
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3558</v>
+        <v>-3.1448</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2931</v>
+        <v>-2.1935</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0626</v>
+        <v>-0.9513</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5766</v>
@@ -1386,13 +1386,13 @@
         <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8902</v>
+        <v>-0.6793</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4328</v>
+        <v>-0.3332</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4574</v>
+        <v>-0.3461</v>
       </c>
       <c r="V12" t="n">
         <v>0.2795</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.804</v>
+        <v>-4.0822</v>
       </c>
       <c r="E13" t="n">
         <v>-1.1211</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6828</v>
+        <v>-2.9611</v>
       </c>
       <c r="G13" t="n">
         <v>0.8263</v>
@@ -1464,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6493</v>
+        <v>0.371</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6493</v>
+        <v>0.371</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3321</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.7427</v>
+        <v>-10.3324</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2617</v>
+        <v>-4.9626</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.4811</v>
+        <v>-5.3698</v>
       </c>
       <c r="G14" t="n">
         <v>-5.9669</v>
@@ -1542,13 +1542,13 @@
         <v>0.3895</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7758</v>
+        <v>-0.3655</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8657</v>
+        <v>-0.5667</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.2012</v>
       </c>
       <c r="V14" t="n">
         <v>-2.4421</v>
@@ -1575,16 +1575,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.0455</v>
+        <v>-12.5563</v>
       </c>
       <c r="E15" t="n">
-        <v>3.431299999999999</v>
+        <v>3.531199999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.4768</v>
+        <v>-16.0872</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8582999999999998</v>
+        <v>0.8583000000000016</v>
       </c>
       <c r="H15" t="n">
         <v>5.905599999999998</v>
@@ -1620,13 +1620,13 @@
         <v>14.6053</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.928</v>
+        <v>-5.438899999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.890700000000001</v>
+        <v>-5.7912</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.03720000000000011</v>
+        <v>0.3524999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-4.0809</v>
